--- a/output/pdf_financials_xlsx/STCQ.xlsx
+++ b/output/pdf_financials_xlsx/STCQ.xlsx
@@ -484,20 +484,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>0.038115</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>-0.551679</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -506,25 +500,17 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -538,20 +524,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>0.038115</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-0.551679</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -560,25 +540,17 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>-0.005269</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-0.003537</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>-0.000697</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-0.000425</v>
       </c>
     </row>
     <row r="8">
@@ -587,25 +559,17 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -614,25 +578,17 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -665,20 +621,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="3" t="n">
+        <v>-1.215484</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-1.056313</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-1.038789</v>
       </c>
     </row>
     <row r="12">
@@ -687,25 +637,17 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -714,25 +656,17 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -741,25 +675,17 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -768,25 +694,17 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>-5.516672</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.041009</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-0.056109</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1.680236</v>
       </c>
     </row>
     <row r="16">
@@ -795,25 +713,17 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-8.219849999999999</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-1.196748</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-1.108807</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.63914</v>
       </c>
     </row>
     <row r="17">
@@ -822,25 +732,17 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -903,25 +805,17 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-8.219849999999999</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-1.196748</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-1.108807</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.63914</v>
       </c>
     </row>
     <row r="21">
@@ -930,25 +824,17 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -960,20 +846,14 @@
       <c r="B22" s="3" t="n">
         <v>1.363441</v>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1020,25 +900,17 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1074,25 +946,17 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-8.219849999999999</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-1.196748</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-1.108807</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.63914</v>
       </c>
     </row>
     <row r="28">
@@ -1104,20 +968,14 @@
       <c r="B28" s="3" t="n">
         <v>0.019059</v>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1126,25 +984,17 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-8.200791000000001</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-1.196748</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-1.108807</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.63914</v>
       </c>
     </row>
     <row r="30">
@@ -1158,15 +1008,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C30" s="3" t="n">
+        <v>-3139.834710743802</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>200.9877120571927</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -1180,25 +1026,17 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1212,15 +1050,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C32" s="3" t="n">
+        <v>-3139.834710743802</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>200.9877120571927</v>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
@@ -1241,10 +1075,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>1.102863</v>
@@ -1262,25 +1094,17 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1289,25 +1113,17 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1.102863</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0.380763</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.41176</v>
       </c>
     </row>
     <row r="37">
@@ -1316,25 +1132,17 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1343,25 +1151,17 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1373,20 +1173,14 @@
       <c r="B39" s="3" t="n">
         <v>0.408715</v>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1396,22 +1190,16 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.107717</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0.019428</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0.024573</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.042705</v>
       </c>
     </row>
     <row r="41">
@@ -1420,25 +1208,17 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.516432</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.019428</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0.024573</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.042705</v>
       </c>
     </row>
     <row r="42">
@@ -1447,25 +1227,17 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1474,25 +1246,17 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1501,25 +1265,17 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1528,25 +1284,17 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1555,25 +1303,17 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1582,25 +1322,17 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1609,25 +1341,17 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>2.179732</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1.300752</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1662,20 +1386,14 @@
       <c r="B50" s="3" t="n">
         <v>0.638856</v>
       </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1684,25 +1402,17 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1711,25 +1421,17 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1738,25 +1440,17 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1765,25 +1459,17 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1819,25 +1505,17 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1846,25 +1524,17 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1873,25 +1543,17 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1900,25 +1562,17 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1927,25 +1581,17 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1954,25 +1600,17 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0.408715</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1984,10 +1622,8 @@
       <c r="B62" s="3" t="n">
         <v>1.047571</v>
       </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C62" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
@@ -2025,25 +1661,17 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2052,25 +1680,17 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2079,25 +1699,17 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0.000136</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0.016643</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2106,25 +1718,17 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2152,25 +1756,17 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2179,25 +1775,17 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2206,25 +1794,17 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2233,25 +1813,17 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2260,25 +1832,17 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2287,25 +1851,17 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2314,25 +1870,17 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0.001813</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2364,25 +1912,17 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2391,25 +1931,17 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2418,25 +1950,17 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2472,25 +1996,17 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2499,25 +2015,17 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2526,25 +2034,17 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2553,25 +2053,17 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2580,25 +2072,17 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0.036713</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2610,10 +2094,8 @@
       <c r="B86" s="3" t="n">
         <v>0.036713</v>
       </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
@@ -2651,25 +2133,17 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>61.756937</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>61.756937</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>62.541201</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>62.541201</v>
       </c>
     </row>
     <row r="89">
@@ -2678,25 +2152,17 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2724,25 +2190,17 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2751,25 +2209,17 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2778,25 +2228,17 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2824,25 +2266,17 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2851,25 +2285,17 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>3.491273</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>2.294525</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>1.969982</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>2.609122</v>
       </c>
     </row>
     <row r="97">
@@ -2904,25 +2330,17 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-8.219849999999999</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-1.196748</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-1.108807</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>0.63914</v>
       </c>
     </row>
     <row r="100">
@@ -2934,20 +2352,14 @@
       <c r="B100" s="3" t="n">
         <v>0.019059</v>
       </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2956,23 +2368,17 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2981,25 +2387,17 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3008,25 +2406,17 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.017327</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>-0.020141</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0.019808</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0.001483</v>
       </c>
     </row>
     <row r="104">
@@ -3054,25 +2444,17 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3081,25 +2463,17 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.039994</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.047372</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.061132</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.009379999999999999</v>
       </c>
     </row>
     <row r="107">
@@ -3108,25 +2482,17 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.025823</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3135,25 +2501,17 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3162,25 +2520,17 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3189,25 +2539,17 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3216,25 +2558,17 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3243,25 +2577,17 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3270,25 +2596,17 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3297,10 +2615,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>-0.13321</v>
@@ -3318,25 +2634,17 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3345,25 +2653,17 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3372,25 +2672,17 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3399,25 +2691,17 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3426,20 +2710,16 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>1.359936</v>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
@@ -3453,25 +2733,17 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3480,25 +2752,17 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3507,25 +2771,17 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3534,25 +2790,17 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3561,25 +2809,17 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3588,25 +2828,17 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3615,25 +2847,17 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3669,25 +2893,17 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3696,10 +2912,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>-0.039813</v>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
@@ -3740,25 +2954,17 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3767,25 +2973,17 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.156554</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-1.431326</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.7221</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>0.030997</v>
       </c>
     </row>
     <row r="133">
@@ -3794,10 +2992,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>2.534189</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>1.102863</v>
@@ -3815,25 +3011,17 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3842,25 +3030,17 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-1.163569</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-1.431326</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.8521</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>0.030997</v>
       </c>
     </row>
   </sheetData>
@@ -3999,7 +3179,11 @@
           <t>Sales tax receivable</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -4633,7 +3817,11 @@
           <t>Sales tax receivable 6</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>0.007717</v>
       </c>
@@ -5087,7 +4275,11 @@
           <t>Due to related parties 16</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.000136</v>
       </c>
@@ -5449,7 +4641,11 @@
           <t>Net income (loss) for the year $</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -5721,7 +4917,11 @@
           <t>Prepaid expenses</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>0.017327</v>
       </c>
@@ -6153,7 +5353,11 @@
           <t>Net loss for the year $</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>-8.219849999999999</v>
       </c>
@@ -6325,7 +5529,11 @@
           <t>Other receivable</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -6949,7 +6157,11 @@
           <t>Share-based payments</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>0.025823</v>
       </c>
@@ -7379,7 +6591,11 @@
           <t>Cash flows from (used in) investing activities total</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E99" s="5" t="n">
         <v>1.359936</v>
       </c>
@@ -7487,7 +6703,11 @@
           <t>Cash flows from (used in) financing activities total</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="n">
         <v>-0.039813</v>
       </c>
@@ -7559,7 +6779,11 @@
           <t>Change in cash for the year</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E104" s="5" t="n">
         <v>0.156554</v>
       </c>
@@ -7631,7 +6855,11 @@
           <t>Cash, end of the year $</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E106" s="5" t="n">
         <v>2.534189</v>
       </c>
@@ -7871,7 +7099,11 @@
           <t>Loss before other income (expenses)</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -7939,7 +7171,11 @@
           <t>Interest expense and bank charges</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -7971,7 +7207,11 @@
           <t>Foreign exchange (loss) gain</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -8075,7 +7315,11 @@
           <t>Total other income (expenses)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E119" s="5" t="n">
         <v>-5.525951</v>
       </c>
@@ -8639,7 +7883,11 @@
           <t>Revenue total</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -9367,7 +8615,11 @@
           <t>Interest expense and bank charges 10</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E155" s="5" t="n">
         <v>-0.005269</v>
       </c>
@@ -9473,7 +8725,11 @@
           <t>Other income</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E158" s="5" t="n">
         <v>0.009279000000000001</v>
       </c>
@@ -9545,7 +8801,11 @@
           <t>Foreign exchange gain</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/STCQ.xlsx
+++ b/output/pdf_financials_xlsx/STCQ.xlsx
@@ -431,6 +431,13 @@
   </sheetPr>
   <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/STCQ.xlsx
+++ b/output/pdf_financials_xlsx/STCQ.xlsx
@@ -548,16 +548,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.005269</v>
+        <v>0.005269</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-0.003537</v>
+        <v>0.003537</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>-0.000697</v>
+        <v>0.000697</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-0.000425</v>
+        <v>0.000425</v>
       </c>
     </row>
     <row r="8">
@@ -664,16 +664,16 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -740,16 +740,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -3061,7 +3061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7075,10 +7075,8 @@
           <t>OperatingExpense</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E112" s="5" t="n">
+        <v>1.07777</v>
       </c>
       <c r="F112" s="5" t="n">
         <v>1.253599</v>
@@ -7189,13 +7187,13 @@
         </is>
       </c>
       <c r="F115" s="5" t="n">
-        <v>-0.003537</v>
+        <v>0.003537</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>-0.000697</v>
+        <v>0.000697</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>-0.000425</v>
+        <v>0.000425</v>
       </c>
     </row>
     <row r="116">
@@ -8547,19 +8545,15 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>T otal operating expenses</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Loss before other expenses</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" s="5" t="n">
-        <v>1.07777</v>
+        <v>-1.07777</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>1.253599</v>
+        <v>-1.215484</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -8580,20 +8574,24 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Loss before other expenses</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
+          <t>Interest expense and bank charges 10</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="n">
-        <v>-1.07777</v>
+        <v>0.005269</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>-1.215484</v>
+        <v>0.003537</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -8619,19 +8617,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Interest expense and bank charges 10</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Loss on sale of subsidiaries 4</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" s="5" t="n">
-        <v>-0.005269</v>
-      </c>
-      <c r="F155" s="5" t="n">
-        <v>-0.003537</v>
+        <v>-4.719708</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -8657,12 +8653,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Loss on sale of subsidiaries 4</t>
+          <t>Impairment loss</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" s="5" t="n">
-        <v>-4.719708</v>
+        <v>-0.231873</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -8693,12 +8689,16 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Impairment loss</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E157" s="5" t="n">
-        <v>-0.231873</v>
+        <v>0.009279000000000001</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -8729,16 +8729,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Change in fair value of investment 5</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" s="5" t="n">
-        <v>0.009279000000000001</v>
+        <v>-0.57838</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -8769,17 +8765,21 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Change in fair value of investment 5</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" s="5" t="n">
-        <v>-0.57838</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>0.022273</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -8805,21 +8805,15 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss from continuing operations</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" s="5" t="n">
+        <v>-6.603721</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>0.022273</v>
+        <v>-1.196748</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -8845,15 +8839,17 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Loss from continuing operations</t>
+          <t>Loss from discontinued operations 20</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" s="5" t="n">
-        <v>-6.603721</v>
-      </c>
-      <c r="F161" s="5" t="n">
-        <v>-1.196748</v>
+        <v>-1.616129</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -8874,22 +8870,20 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>year</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Loss from discontinued operations 20</t>
+          <t>Equity holders of the Parent $</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" s="5" t="n">
-        <v>-1.616129</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.856409</v>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>-1.196748</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -8915,15 +8909,21 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Equity holders of the Parent $</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>Non-controlling Interests</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E163" s="5" t="n">
-        <v>-6.856409</v>
-      </c>
-      <c r="F163" s="5" t="n">
-        <v>-1.196748</v>
+        <v>1.363441</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -8949,21 +8949,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Non-controlling Interests</t>
+          <t>Net loss for the year $</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>1.363441</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.219849999999999</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>-1.196748</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -8984,24 +8982,20 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>Holders of the Parent</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Holders of the Parent from continuing operations $</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" s="5" t="n">
-        <v>-8.219849999999999</v>
+        <v>-1e-08</v>
       </c>
       <c r="F165" s="5" t="n">
-        <v>-1.196748</v>
+        <v>0</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -9027,15 +9021,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Holders of the Parent from continuing operations $</t>
+          <t>from discontinued operations $</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="F166" s="5" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -9061,17 +9057,19 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>from discontinued operations $</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E167" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -9092,24 +9090,20 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Holders of the Parent</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Balance, April 30, 2021 625,196,572 61,756,937 1,778,667 1,595,525 - (60,574,718)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" s="5" t="n">
-        <v>-1e-08</v>
+        <v>9.740534999999999</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>0</v>
+        <v>5.184124</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -9135,15 +9129,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2021 625,196,572 61,756,937 1,778,667 1,595,525 - (60,574,718)</t>
+          <t>Cancellation or expiry of stock options - - (957,961) - - 957,961</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
-      <c r="E169" s="5" t="n">
-        <v>9.740534999999999</v>
-      </c>
-      <c r="F169" s="5" t="n">
-        <v>5.184124</v>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -9169,7 +9167,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Cancellation or expiry of stock options - - (957,961) - - 957,961</t>
+          <t>Expiry of warrants - - - (322,322) 322,322</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -9207,19 +9205,15 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Expiry of warrants - - - (322,322) 322,322</t>
+          <t>WCE shares sold by PED - - - - 101,279 -</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E171" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F171" s="5" t="n">
+        <v>0.298721</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -9245,15 +9239,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>WCE shares sold by PED - - - - 101,279 -</t>
+          <t>Share-based payments - - 25,823 - - -</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>0.298721</v>
+        <v>0.025823</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -9279,17 +9275,15 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Share-based payments - - 25,823 - - -</t>
+          <t>Gain on sale of PED attribute to NCI - - - - - -</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" s="5" t="n">
-        <v>0.025823</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.544765</v>
+      </c>
+      <c r="F173" s="5" t="n">
+        <v>1.544765</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -9315,15 +9309,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Gain on sale of PED attribute to NCI - - - - - -</t>
+          <t>Disposition of PED - - - - (101,279) 5,765,448</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
-      <c r="E174" s="5" t="n">
-        <v>1.544765</v>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F174" s="5" t="n">
-        <v>1.544765</v>
+        <v>-5.664169</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -9349,17 +9345,15 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Disposition of PED - - - - (101,279) 5,765,448</t>
+          <t>Net loss from discontinued operations for the year - - - - - (252,688)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E175" s="5" t="n">
+        <v>-1.616129</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>-5.664169</v>
+        <v>-1.363411</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -9385,15 +9379,17 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Net loss from discontinued operations for the year - - - - - (252,688)</t>
+          <t>Net loss from continuing operations for the year - - - - - (6,603,721)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" s="5" t="n">
-        <v>-1.616129</v>
-      </c>
-      <c r="F176" s="5" t="n">
-        <v>-1.363411</v>
+        <v>-6.603721</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -9419,12 +9415,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Net loss from continuing operations for the year - - - - - (6,603,721)</t>
+          <t>Balance, April 30, 2022 625,196,572 61,756,937 846,529 1,273,203 - (60,385,396)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" s="5" t="n">
-        <v>-6.603721</v>
+        <v>3.491273</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -9455,12 +9451,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2022 625,196,572 61,756,937 846,529 1,273,203 - (60,385,396)</t>
+          <t>Expiry of warrants - - - (1,273,203) - 1,273,203</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" s="5" t="n">
-        <v>3.491273</v>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -9491,7 +9489,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Expiry of warrants - - - (1,273,203) - 1,273,203</t>
+          <t>Cancellation or expiry of stock options - - (255,776) - - 255,776</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -9529,14 +9527,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cancellation or expiry of stock options - - (255,776) - - 255,776</t>
+          <t>Net loss for the year - - - - - (1,196,748)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E180" s="5" t="n">
+        <v>-1.196748</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -9567,12 +9563,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - - (1,196,748)</t>
+          <t>Balance, April 30, 2023 625,196,572 61,756,937 590,753 - - (60,053,165)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" s="5" t="n">
-        <v>-1.196748</v>
+        <v>2.294525</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -9585,42 +9581,6 @@
         </is>
       </c>
       <c r="H181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Shares</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Balance, April 30, 2023 625,196,572 61,756,937 590,753 - - (60,053,165)</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" s="5" t="n">
-        <v>2.294525</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/STCQ.xlsx
+++ b/output/pdf_financials_xlsx/STCQ.xlsx
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.119732</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.590753</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.057523</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -3450,7 +3450,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3722,7 +3726,11 @@
           <t>Reserves 9,10</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -4580,7 +4588,11 @@
           <t>Reserves 12,13</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>2.119732</v>
       </c>

--- a/output/pdf_financials_xlsx/STCQ.xlsx
+++ b/output/pdf_financials_xlsx/STCQ.xlsx
@@ -648,13 +648,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.025668</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.033356</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.049863</v>
       </c>
     </row>
     <row r="13">
@@ -957,13 +957,13 @@
         <v>-8.219849999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.196748</v>
+        <v>-1.222416</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.108807</v>
+        <v>-1.142163</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.63914</v>
+        <v>0.5892770000000001</v>
       </c>
     </row>
     <row r="28">
@@ -995,13 +995,13 @@
         <v>-8.200791000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.196748</v>
+        <v>-1.222416</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.108807</v>
+        <v>-1.142163</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.63914</v>
+        <v>0.5892770000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-3139.834710743802</v>
+        <v>-3207.178276269186</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>200.9877120571927</v>
+        <v>207.0339817176292</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.534189</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>1.102863</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.534189</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>1.102863</v>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.179732</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>1.300752</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">

--- a/output/pdf_financials_xlsx/STCQ.xlsx
+++ b/output/pdf_financials_xlsx/STCQ.xlsx
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-8.219849999999999</v>
+        <v>-6.603721</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-1.196748</v>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-1.616129</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.213936</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.070198</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.181791</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.042358</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -2648,10 +2648,10 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.133498</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.074714</v>
       </c>
     </row>
     <row r="116">
@@ -4970,7 +4970,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -5588,7 +5592,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -8820,7 +8828,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="n">
         <v>-6.603721</v>
       </c>
@@ -8854,7 +8866,11 @@
           <t>Loss from discontinued operations 20</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E161" s="5" t="n">
         <v>-1.616129</v>
       </c>
